--- a/templates/deliverable/example/08_DB표준코드.xlsx
+++ b/templates/deliverable/example/08_DB표준코드.xlsx
@@ -12,11 +12,38 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>DB 표준코드</t>
   </si>
   <si>
+    <t>관리부서명</t>
+  </si>
+  <si>
+    <t>한글코드명</t>
+  </si>
+  <si>
+    <t>영문코드명</t>
+  </si>
+  <si>
+    <t>코드설명</t>
+  </si>
+  <si>
+    <t>데이터타입</t>
+  </si>
+  <si>
+    <t>데이터길이</t>
+  </si>
+  <si>
+    <t>코드값</t>
+  </si>
+  <si>
+    <t>코드값 의미</t>
+  </si>
+  <si>
+    <t>제정일자</t>
+  </si>
+  <si>
     <t>순번</t>
   </si>
   <si>
@@ -26,31 +53,7 @@
     <t>DB명</t>
   </si>
   <si>
-    <t>관리부서명</t>
-  </si>
-  <si>
-    <t>코드명(한글)</t>
-  </si>
-  <si>
-    <t>코드명(영문)</t>
-  </si>
-  <si>
-    <t>데이터타입</t>
-  </si>
-  <si>
-    <t>데이터길이</t>
-  </si>
-  <si>
-    <t>코드값</t>
-  </si>
-  <si>
-    <t>코드값의미</t>
-  </si>
-  <si>
     <t>코드값설명</t>
-  </si>
-  <si>
-    <t>제정일자</t>
   </si>
   <si>
     <t>사용여부</t>
@@ -74,12 +77,12 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="11.0"/>
+      <sz val="14.0"/>
       <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="14.0"/>
+      <sz val="11.0"/>
       <b val="true"/>
     </font>
   </fonts>
@@ -133,8 +136,8 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
   </cellXfs>
 </styleSheet>
@@ -142,23 +145,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="8.0" customWidth="true"/>
-    <col min="2" max="2" width="10.0" customWidth="true"/>
-    <col min="3" max="3" width="10.0" customWidth="true"/>
-    <col min="4" max="4" width="14.0" customWidth="true"/>
-    <col min="5" max="5" width="18.0" customWidth="true"/>
-    <col min="6" max="6" width="18.0" customWidth="true"/>
-    <col min="7" max="7" width="14.0" customWidth="true"/>
-    <col min="8" max="8" width="14.0" customWidth="true"/>
-    <col min="9" max="9" width="10.0" customWidth="true"/>
-    <col min="10" max="10" width="14.0" customWidth="true"/>
-    <col min="11" max="11" width="14.0" customWidth="true"/>
-    <col min="12" max="12" width="12.0" customWidth="true"/>
-    <col min="13" max="13" width="12.0" customWidth="true"/>
+    <col min="1" max="1" width="14.0" customWidth="true"/>
+    <col min="2" max="2" width="14.0" customWidth="true"/>
+    <col min="3" max="3" width="14.0" customWidth="true"/>
+    <col min="4" max="4" width="12.0" customWidth="true"/>
+    <col min="5" max="5" width="14.0" customWidth="true"/>
+    <col min="6" max="6" width="14.0" customWidth="true"/>
+    <col min="7" max="7" width="10.0" customWidth="true"/>
+    <col min="8" max="8" width="16.0" customWidth="true"/>
+    <col min="9" max="9" width="12.0" customWidth="true"/>
+    <col min="10" max="10" width="8.0" customWidth="true"/>
+    <col min="11" max="11" width="10.0" customWidth="true"/>
+    <col min="12" max="12" width="10.0" customWidth="true"/>
+    <col min="13" max="13" width="14.0" customWidth="true"/>
     <col min="14" max="14" width="12.0" customWidth="true"/>
+    <col min="15" max="15" width="12.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -208,6 +212,9 @@
       </c>
       <c r="N2" t="s" s="2">
         <v>14</v>
+      </c>
+      <c r="O2" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -225,6 +232,7 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
